--- a/Web3_Career_Tracker.xlsx
+++ b/Web3_Career_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\susha\Downloads\mission_web3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DB6E8F-8F89-4FC9-BA28-D131DB7498C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F668F891-E98C-477E-9529-0839176B0542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1125,22 +1125,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1450,12 +1450,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="7" max="7" width="68.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
@@ -1500,7 +1500,7 @@
       <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="13" t="s">
@@ -1515,7 +1515,7 @@
       <c r="F2" s="13">
         <v>6</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="18" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -1527,7 +1527,7 @@
       <c r="J2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="15"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="14"/>
@@ -1560,37 +1560,37 @@
       <c r="K4" s="14"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
-        <v>1</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="21">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="21">
         <v>1.5</v>
       </c>
-      <c r="E5" s="19">
-        <v>1</v>
-      </c>
-      <c r="F5" s="19">
+      <c r="E5" s="21">
+        <v>1</v>
+      </c>
+      <c r="F5" s="21">
         <v>2.5</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="19" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="21"/>
+      <c r="I5" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="19"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="20"/>
@@ -1611,7 +1611,7 @@
       <c r="A7" s="13">
         <v>2</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="13" t="s">
@@ -1626,7 +1626,7 @@
       <c r="F7" s="13">
         <v>6</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="18" t="s">
         <v>25</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -1638,7 +1638,7 @@
       <c r="J7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="15"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
@@ -1692,7 +1692,7 @@
       <c r="A10" s="13">
         <v>3</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="13" t="s">
@@ -1707,7 +1707,7 @@
       <c r="F10" s="13">
         <v>6</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="18" t="s">
         <v>32</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -1719,7 +1719,7 @@
       <c r="J10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="15"/>
+      <c r="K10" s="18"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
@@ -1773,7 +1773,7 @@
       <c r="A13" s="13">
         <v>4</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="18" t="s">
         <v>37</v>
       </c>
       <c r="C13" s="13" t="s">
@@ -1788,7 +1788,7 @@
       <c r="F13" s="13">
         <v>6</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="18" t="s">
         <v>38</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -1800,7 +1800,7 @@
       <c r="J13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="15"/>
+      <c r="K13" s="18"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
@@ -1854,7 +1854,7 @@
       <c r="A16" s="13">
         <v>5</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="18" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="13" t="s">
@@ -1869,7 +1869,7 @@
       <c r="F16" s="13">
         <v>6</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="18" t="s">
         <v>45</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -1881,7 +1881,7 @@
       <c r="J16" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="K16" s="18"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
@@ -1935,7 +1935,7 @@
       <c r="A19" s="13">
         <v>6</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="13" t="s">
@@ -1950,7 +1950,7 @@
       <c r="F19" s="13">
         <v>6</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="18" t="s">
         <v>52</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -1962,7 +1962,7 @@
       <c r="J19" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K19" s="15"/>
+      <c r="K19" s="18"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
@@ -2016,7 +2016,7 @@
       <c r="A22" s="13">
         <v>7</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C22" s="13" t="s">
@@ -2031,7 +2031,7 @@
       <c r="F22" s="13">
         <v>6</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="18" t="s">
         <v>58</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -2043,7 +2043,7 @@
       <c r="J22" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="15"/>
+      <c r="K22" s="18"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="14"/>
@@ -2097,7 +2097,7 @@
       <c r="A25" s="13">
         <v>8</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="18" t="s">
         <v>64</v>
       </c>
       <c r="C25" s="13" t="s">
@@ -2112,7 +2112,7 @@
       <c r="F25" s="13">
         <v>6</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="18" t="s">
         <v>65</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -2124,7 +2124,7 @@
       <c r="J25" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="K25" s="18"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
@@ -2178,7 +2178,7 @@
       <c r="A28" s="13">
         <v>9</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C28" s="13" t="s">
@@ -2193,7 +2193,7 @@
       <c r="F28" s="13">
         <v>8</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="18" t="s">
         <v>72</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -2205,7 +2205,7 @@
       <c r="J28" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K28" s="15"/>
+      <c r="K28" s="18"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
@@ -2274,7 +2274,7 @@
       <c r="A32" s="13">
         <v>10</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="18" t="s">
         <v>79</v>
       </c>
       <c r="C32" s="13" t="s">
@@ -2289,7 +2289,7 @@
       <c r="F32" s="13">
         <v>8</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="18" t="s">
         <v>80</v>
       </c>
       <c r="H32" s="4" t="s">
@@ -2301,7 +2301,7 @@
       <c r="J32" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K32" s="15"/>
+      <c r="K32" s="18"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
@@ -2421,7 +2421,7 @@
       <c r="A37" s="13">
         <v>12</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="18" t="s">
         <v>90</v>
       </c>
       <c r="C37" s="13" t="s">
@@ -2436,7 +2436,7 @@
       <c r="F37" s="13">
         <v>6</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="18" t="s">
         <v>91</v>
       </c>
       <c r="H37" s="4" t="s">
@@ -2448,7 +2448,7 @@
       <c r="J37" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K37" s="15"/>
+      <c r="K37" s="18"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="14"/>
@@ -2502,7 +2502,7 @@
       <c r="A40" s="13">
         <v>13</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="18" t="s">
         <v>96</v>
       </c>
       <c r="C40" s="13" t="s">
@@ -2517,7 +2517,7 @@
       <c r="F40" s="13">
         <v>6.5</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="18" t="s">
         <v>97</v>
       </c>
       <c r="H40" s="4" t="s">
@@ -2529,7 +2529,7 @@
       <c r="J40" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K40" s="15"/>
+      <c r="K40" s="18"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="14"/>
@@ -2583,7 +2583,7 @@
       <c r="A43" s="13">
         <v>14</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="18" t="s">
         <v>101</v>
       </c>
       <c r="C43" s="13" t="s">
@@ -2598,7 +2598,7 @@
       <c r="F43" s="13">
         <v>6.5</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="G43" s="18" t="s">
         <v>102</v>
       </c>
       <c r="H43" s="4" t="s">
@@ -2610,7 +2610,7 @@
       <c r="J43" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K43" s="15"/>
+      <c r="K43" s="18"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="14"/>
@@ -2664,7 +2664,7 @@
       <c r="A46" s="13">
         <v>15</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C46" s="13" t="s">
@@ -2679,7 +2679,7 @@
       <c r="F46" s="13">
         <v>6.5</v>
       </c>
-      <c r="G46" s="15" t="s">
+      <c r="G46" s="18" t="s">
         <v>108</v>
       </c>
       <c r="H46" s="4" t="s">
@@ -2691,7 +2691,7 @@
       <c r="J46" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K46" s="15"/>
+      <c r="K46" s="18"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="14"/>
@@ -2745,7 +2745,7 @@
       <c r="A49" s="13">
         <v>16</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="18" t="s">
         <v>114</v>
       </c>
       <c r="C49" s="13" t="s">
@@ -2760,7 +2760,7 @@
       <c r="F49" s="13">
         <v>6.5</v>
       </c>
-      <c r="G49" s="15" t="s">
+      <c r="G49" s="18" t="s">
         <v>115</v>
       </c>
       <c r="H49" s="4" t="s">
@@ -2772,7 +2772,7 @@
       <c r="J49" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K49" s="15"/>
+      <c r="K49" s="18"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="14"/>
@@ -2826,7 +2826,7 @@
       <c r="A52" s="13">
         <v>17</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="18" t="s">
         <v>121</v>
       </c>
       <c r="C52" s="13" t="s">
@@ -2841,7 +2841,7 @@
       <c r="F52" s="13">
         <v>6.5</v>
       </c>
-      <c r="G52" s="15" t="s">
+      <c r="G52" s="18" t="s">
         <v>122</v>
       </c>
       <c r="H52" s="4" t="s">
@@ -2853,7 +2853,7 @@
       <c r="J52" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K52" s="15"/>
+      <c r="K52" s="18"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="14"/>
@@ -2973,7 +2973,7 @@
       <c r="A57" s="13">
         <v>19</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="18" t="s">
         <v>134</v>
       </c>
       <c r="C57" s="13" t="s">
@@ -2988,7 +2988,7 @@
       <c r="F57" s="13">
         <v>6.5</v>
       </c>
-      <c r="G57" s="15" t="s">
+      <c r="G57" s="18" t="s">
         <v>135</v>
       </c>
       <c r="H57" s="4" t="s">
@@ -3000,7 +3000,7 @@
       <c r="J57" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K57" s="15"/>
+      <c r="K57" s="18"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
@@ -3054,7 +3054,7 @@
       <c r="A60" s="13">
         <v>20</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="18" t="s">
         <v>140</v>
       </c>
       <c r="C60" s="13" t="s">
@@ -3069,7 +3069,7 @@
       <c r="F60" s="13">
         <v>6.5</v>
       </c>
-      <c r="G60" s="15" t="s">
+      <c r="G60" s="18" t="s">
         <v>141</v>
       </c>
       <c r="H60" s="4" t="s">
@@ -3081,7 +3081,7 @@
       <c r="J60" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K60" s="15"/>
+      <c r="K60" s="18"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
@@ -3399,7 +3399,7 @@
       <c r="A71" s="13">
         <v>25</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="18" t="s">
         <v>169</v>
       </c>
       <c r="C71" s="13" t="s">
@@ -3414,7 +3414,7 @@
       <c r="F71" s="13">
         <v>7</v>
       </c>
-      <c r="G71" s="15" t="s">
+      <c r="G71" s="18" t="s">
         <v>170</v>
       </c>
       <c r="H71" s="4" t="s">
@@ -3426,7 +3426,7 @@
       <c r="J71" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K71" s="15"/>
+      <c r="K71" s="18"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="14"/>
@@ -3675,52 +3675,52 @@
       <c r="K79" s="6"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="18">
+      <c r="A80" s="15">
         <v>29</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C80" s="18" t="s">
+      <c r="C80" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="D80" s="18">
+      <c r="D80" s="15">
         <v>2</v>
       </c>
-      <c r="E80" s="18">
+      <c r="E80" s="15">
         <v>6</v>
       </c>
-      <c r="F80" s="18">
+      <c r="F80" s="15">
         <v>8</v>
       </c>
-      <c r="G80" s="16" t="s">
+      <c r="G80" s="17" t="s">
         <v>196</v>
       </c>
       <c r="H80" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="I80" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J80" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="K80" s="16"/>
+      <c r="I80" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" s="17"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="17"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
+      <c r="A81" s="16"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="16"/>
       <c r="H81" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
+      <c r="I81" s="16"/>
+      <c r="J81" s="16"/>
+      <c r="K81" s="16"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
@@ -3822,52 +3822,52 @@
       <c r="K84" s="6"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="18">
+      <c r="A85" s="15">
         <v>31</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B85" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="D85" s="18">
+      <c r="D85" s="15">
         <v>1.5</v>
       </c>
-      <c r="E85" s="18">
+      <c r="E85" s="15">
         <v>6.5</v>
       </c>
-      <c r="F85" s="18">
+      <c r="F85" s="15">
         <v>8</v>
       </c>
-      <c r="G85" s="16" t="s">
+      <c r="G85" s="17" t="s">
         <v>209</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I85" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J85" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="K85" s="16"/>
+      <c r="I85" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K85" s="17"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="17"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
-      <c r="D86" s="17"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="17"/>
-      <c r="G86" s="17"/>
+      <c r="A86" s="16"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="16"/>
       <c r="H86" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="I86" s="17"/>
-      <c r="J86" s="17"/>
-      <c r="K86" s="17"/>
+      <c r="I86" s="16"/>
+      <c r="J86" s="16"/>
+      <c r="K86" s="16"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
@@ -3903,52 +3903,52 @@
       <c r="K87" s="6"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="18">
+      <c r="A88" s="15">
         <v>32</v>
       </c>
-      <c r="B88" s="16" t="s">
+      <c r="B88" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="C88" s="18" t="s">
+      <c r="C88" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="D88" s="18">
-        <v>1</v>
-      </c>
-      <c r="E88" s="18">
+      <c r="D88" s="15">
+        <v>1</v>
+      </c>
+      <c r="E88" s="15">
         <v>7</v>
       </c>
-      <c r="F88" s="18">
+      <c r="F88" s="15">
         <v>8</v>
       </c>
-      <c r="G88" s="16" t="s">
+      <c r="G88" s="17" t="s">
         <v>216</v>
       </c>
       <c r="H88" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="I88" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J88" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="K88" s="16"/>
+      <c r="I88" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K88" s="17"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="17"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="17"/>
-      <c r="G89" s="17"/>
+      <c r="A89" s="16"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="16"/>
       <c r="H89" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="I89" s="17"/>
-      <c r="J89" s="17"/>
-      <c r="K89" s="17"/>
+      <c r="I89" s="16"/>
+      <c r="J89" s="16"/>
+      <c r="K89" s="16"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
@@ -3984,85 +3984,85 @@
       <c r="K90" s="6"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="18">
+      <c r="A91" s="15">
         <v>33</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="C91" s="18" t="s">
+      <c r="C91" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="D91" s="18">
+      <c r="D91" s="15">
         <v>2</v>
       </c>
-      <c r="E91" s="18">
+      <c r="E91" s="15">
         <v>6</v>
       </c>
-      <c r="F91" s="18">
+      <c r="F91" s="15">
         <v>8</v>
       </c>
-      <c r="G91" s="16" t="s">
+      <c r="G91" s="17" t="s">
         <v>222</v>
       </c>
       <c r="H91" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="I91" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J91" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="K91" s="16"/>
+      <c r="I91" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J91" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K91" s="17"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="17"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="17"/>
-      <c r="E92" s="17"/>
-      <c r="F92" s="17"/>
-      <c r="G92" s="17"/>
+      <c r="A92" s="16"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
       <c r="H92" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="I92" s="17"/>
-      <c r="J92" s="17"/>
-      <c r="K92" s="17"/>
+      <c r="I92" s="16"/>
+      <c r="J92" s="16"/>
+      <c r="K92" s="16"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="19">
+      <c r="A93" s="21">
         <v>33</v>
       </c>
-      <c r="B93" s="21" t="s">
+      <c r="B93" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="D93" s="19">
-        <v>1</v>
-      </c>
-      <c r="E93" s="19">
-        <v>1</v>
-      </c>
-      <c r="F93" s="19">
+      <c r="D93" s="21">
+        <v>1</v>
+      </c>
+      <c r="E93" s="21">
+        <v>1</v>
+      </c>
+      <c r="F93" s="21">
         <v>2</v>
       </c>
-      <c r="G93" s="21" t="s">
+      <c r="G93" s="19" t="s">
         <v>226</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="I93" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J93" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="K93" s="21"/>
+      <c r="I93" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K93" s="19"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="20"/>
@@ -4149,7 +4149,7 @@
       <c r="A97" s="13">
         <v>35</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="18" t="s">
         <v>233</v>
       </c>
       <c r="C97" s="13" t="s">
@@ -4164,7 +4164,7 @@
       <c r="F97" s="13">
         <v>6</v>
       </c>
-      <c r="G97" s="15" t="s">
+      <c r="G97" s="18" t="s">
         <v>234</v>
       </c>
       <c r="H97" s="4" t="s">
@@ -4176,7 +4176,7 @@
       <c r="J97" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K97" s="15"/>
+      <c r="K97" s="18"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="14"/>
@@ -4194,37 +4194,37 @@
       <c r="K98" s="14"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="19">
+      <c r="A99" s="21">
         <v>35</v>
       </c>
-      <c r="B99" s="21" t="s">
+      <c r="B99" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C99" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="D99" s="19">
-        <v>1</v>
-      </c>
-      <c r="E99" s="19">
-        <v>1</v>
-      </c>
-      <c r="F99" s="19">
+      <c r="D99" s="21">
+        <v>1</v>
+      </c>
+      <c r="E99" s="21">
+        <v>1</v>
+      </c>
+      <c r="F99" s="21">
         <v>2</v>
       </c>
-      <c r="G99" s="21" t="s">
+      <c r="G99" s="19" t="s">
         <v>238</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="I99" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J99" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="K99" s="21"/>
+      <c r="I99" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J99" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K99" s="19"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="20"/>
@@ -4242,52 +4242,52 @@
       <c r="K100" s="20"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="18">
+      <c r="A101" s="15">
         <v>36</v>
       </c>
-      <c r="B101" s="16" t="s">
+      <c r="B101" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="C101" s="18" t="s">
+      <c r="C101" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="D101" s="18">
-        <v>1</v>
-      </c>
-      <c r="E101" s="18">
+      <c r="D101" s="15">
+        <v>1</v>
+      </c>
+      <c r="E101" s="15">
         <v>5</v>
       </c>
-      <c r="F101" s="18">
+      <c r="F101" s="15">
         <v>6</v>
       </c>
-      <c r="G101" s="16" t="s">
+      <c r="G101" s="17" t="s">
         <v>242</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="I101" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J101" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="K101" s="16"/>
+      <c r="I101" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J101" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="17"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="17"/>
-      <c r="B102" s="17"/>
-      <c r="C102" s="17"/>
-      <c r="D102" s="17"/>
-      <c r="E102" s="17"/>
-      <c r="F102" s="17"/>
-      <c r="G102" s="17"/>
+      <c r="A102" s="16"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="16"/>
       <c r="H102" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="I102" s="17"/>
-      <c r="J102" s="17"/>
-      <c r="K102" s="17"/>
+      <c r="I102" s="16"/>
+      <c r="J102" s="16"/>
+      <c r="K102" s="16"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
@@ -4324,31 +4324,214 @@
     </row>
   </sheetData>
   <mergeCells count="280">
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="K101:K102"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="J46:J47"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K88:K89"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="K93:K94"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="K99:K100"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="G97:G98"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="F101:F102"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="K52:K53"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="J57:J58"/>
+    <mergeCell ref="K80:K81"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="K71:K72"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="K32:K33"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="E101:E102"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="J88:J89"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="G101:G102"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="J93:J94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="J99:J100"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="J101:J102"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G88:G89"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="J91:J92"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K57:K58"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="J28:J30"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="K85:K86"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="K28:K30"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="F91:F92"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="G93:G94"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="F97:F98"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="D93:D94"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F93:F94"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="K60:K61"/>
     <mergeCell ref="F28:F30"/>
@@ -4373,22 +4556,47 @@
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="J19:J20"/>
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="J43:J44"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="K101:K102"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="G85:G86"/>
     <mergeCell ref="K97:K98"/>
     <mergeCell ref="A93:A94"/>
-    <mergeCell ref="J52:J53"/>
     <mergeCell ref="E71:E72"/>
-    <mergeCell ref="J5:J6"/>
     <mergeCell ref="G71:G72"/>
-    <mergeCell ref="B22:B23"/>
     <mergeCell ref="J97:J98"/>
-    <mergeCell ref="K16:K17"/>
     <mergeCell ref="B85:B86"/>
     <mergeCell ref="I80:I81"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="B28:B30"/>
     <mergeCell ref="K49:K50"/>
     <mergeCell ref="D28:D30"/>
     <mergeCell ref="E43:E44"/>
@@ -4396,214 +4604,6 @@
     <mergeCell ref="G43:G44"/>
     <mergeCell ref="F80:F81"/>
     <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="D93:D94"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="G93:G94"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="F97:F98"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="K85:K86"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="K28:K30"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="F91:F92"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="J91:J92"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="K46:K47"/>
-    <mergeCell ref="K40:K41"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K57:K58"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E91:E92"/>
-    <mergeCell ref="J28:J30"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="G101:G102"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="J93:J94"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="J99:J100"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="J101:J102"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="I60:I61"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="J71:J72"/>
-    <mergeCell ref="E101:E102"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="J88:J89"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="K52:K53"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="J57:J58"/>
-    <mergeCell ref="K80:K81"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="K71:K72"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="F101:F102"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F93:F94"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G97:G98"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="K32:K33"/>
-    <mergeCell ref="K88:K89"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="K93:K94"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="K99:K100"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
